--- a/AC_2018/AC_027_027-Choppadandi_(SC).xlsx
+++ b/AC_2018/AC_027_027-Choppadandi_(SC).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,32 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +177,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,11 +563,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -519,107 +617,112 @@
           <t>PS_No</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PS_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Bodiga Shobha Galanna</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Manda Ravindar</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Medipally Sathyam</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Ravi Shankar Sunke</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Akkenapally Yesuratnam</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Kanakam Vamshi</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Kanuka Ramesh</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Chiluka Lingaiah</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Bolli Kishan</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Uppuleti Laxman</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Dasari Vidyasagar</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Boddu Narsaiah</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Bollampelly Ailaiah</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Candidate_15</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Total_Valid_Votes</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Rejected_Votes</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Checksum_Diff</t>
         </is>
@@ -629,166 +732,180 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>1</v>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Sarvareddipalli</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>285</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>519</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4" t="n">
         <v>524</v>
       </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <f>SUM(C6:Q6)-R6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>2</v>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Sarvareddipalli</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>297</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="n">
         <v>533</v>
       </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
         <v>541</v>
       </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <f>SUM(C7:Q7)-R7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>3</v>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Narsimulapalli</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>272</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
       </c>
@@ -799,406 +916,442 @@
         <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>509</v>
       </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>513</v>
       </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <f>SUM(C8:Q8)-R8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>4</v>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Burgupalli</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>534</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M9" s="4" t="n">
         <v>2</v>
       </c>
       <c r="N9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>912</v>
       </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>921</v>
       </c>
-      <c r="U9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V9" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="W9" s="4">
+        <f>SUM(C9:Q9)-R9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>5</v>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Burgupalli</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>179</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>540</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>925</v>
       </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>941</v>
       </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V10" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="W10" s="4">
+        <f>SUM(C10:Q10)-R10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>6</v>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Kondaiahpalli</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>317</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="L11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>685</v>
       </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>695</v>
       </c>
-      <c r="U11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="W11" s="4">
+        <f>SUM(C11:Q11)-R11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Ryalapalli</t>
+        </is>
       </c>
       <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>305</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="K12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>784</v>
       </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>791</v>
       </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V12" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="W12" s="4">
+        <f>SUM(C12:Q12)-R12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Ryalapalli</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>390</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>628</v>
       </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>633</v>
       </c>
-      <c r="U13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="W13" s="4">
+        <f>SUM(C13:Q13)-R13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Kachireddipalli</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>172</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>532</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>2</v>
@@ -1207,197 +1360,215 @@
         <v>2</v>
       </c>
       <c r="M14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>790</v>
       </c>
-      <c r="R14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>798</v>
       </c>
-      <c r="U14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
+      </c>
+      <c r="W14" s="4">
+        <f>SUM(C14:Q14)-R14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Venkataipalli</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="D15" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>451</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="N15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R15" s="4" t="n">
         <v>788</v>
       </c>
-      <c r="R15" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="S15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
         <v>798</v>
       </c>
-      <c r="U15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" s="4" t="n">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <f>SUM(C15:Q15)-R15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Narayanpur</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>334</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>616</v>
       </c>
-      <c r="R16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4" t="n">
         <v>625</v>
       </c>
-      <c r="U16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V16" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <f>SUM(C16:Q16)-R16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Narayanpur</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="D17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>184</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>409</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" s="4" t="n">
         <v>0</v>
       </c>
@@ -1414,14 +1585,14 @@
         <v>0</v>
       </c>
       <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="P17" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="P17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
@@ -1429,203 +1600,221 @@
         <v>0</v>
       </c>
       <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>735</v>
       </c>
-      <c r="U17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V17" s="4" t="n">
-        <v>675</v>
+        <v>0</v>
+      </c>
+      <c r="W17" s="4">
+        <f>SUM(C17:Q17)-R17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>30</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Islampur</t>
+        </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>30</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>379</v>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>606</v>
       </c>
-      <c r="R18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4" t="n">
         <v>619</v>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" s="4" t="n">
-        <v>-32</v>
+        <v>0</v>
+      </c>
+      <c r="W18" s="4">
+        <f>SUM(C18:Q18)-R18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Laxmidedvipalli</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="D19" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>490</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>1900</v>
       </c>
-      <c r="R19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>906</v>
       </c>
-      <c r="U19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="4" t="n">
-        <v>-998</v>
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <f>SUM(C19:Q19)-R19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>32</v>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Laxmidedvipalli</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D20" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="E20" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>334</v>
       </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
@@ -1633,52 +1822,58 @@
         <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>606</v>
       </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" s="4" t="n">
-        <v>638</v>
+        <v>0</v>
+      </c>
+      <c r="W20" s="4">
+        <f>SUM(C20:Q20)-R20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Gangadhara</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" s="4" t="n">
         <v>0</v>
       </c>
@@ -1686,58 +1881,64 @@
         <v>0</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="R21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>446</v>
       </c>
-      <c r="U21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V21" s="4" t="n">
-        <v>143</v>
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
+        <f>SUM(C21:Q21)-R21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Gangadhara</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="D22" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>390</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
       </c>
@@ -1763,117 +1964,129 @@
         <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4" t="n">
         <v>670</v>
       </c>
-      <c r="R22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>678</v>
       </c>
-      <c r="U22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <f>SUM(C22:Q22)-R22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Gangadhara</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="D23" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>402</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>2</v>
       </c>
       <c r="N23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4" t="n">
         <v>802</v>
       </c>
-      <c r="R23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>813</v>
       </c>
-      <c r="U23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V23" s="4" t="n">
-        <v>-48</v>
+        <v>0</v>
+      </c>
+      <c r="W23" s="4">
+        <f>SUM(C23:Q23)-R23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>36</v>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Mangapeta H/o Gangadhara</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
         <v>36</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>605</v>
       </c>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
       </c>
@@ -1899,49 +2112,55 @@
         <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4" t="n">
         <v>819</v>
       </c>
-      <c r="R24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>835</v>
       </c>
-      <c r="U24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V24" s="4" t="n">
-        <v>-21</v>
+        <v>0</v>
+      </c>
+      <c r="W24" s="4">
+        <f>SUM(C24:Q24)-R24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>37</v>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Nagireddipur</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>37</v>
       </c>
       <c r="D25" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>165</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>649</v>
       </c>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" s="4" t="n">
         <v>0</v>
       </c>
@@ -1964,64 +2183,70 @@
         <v>0</v>
       </c>
       <c r="P25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>895</v>
       </c>
-      <c r="R25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>906</v>
       </c>
-      <c r="U25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" s="4" t="n">
-        <v>44</v>
+        <v>0</v>
+      </c>
+      <c r="W25" s="4">
+        <f>SUM(C25:Q25)-R25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>38</v>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Nagireddipur</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>38</v>
       </c>
       <c r="D26" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>220</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>485</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I26" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="4" t="n">
         <v>0</v>
       </c>
@@ -2029,55 +2254,61 @@
         <v>0</v>
       </c>
       <c r="O26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="4" t="n">
         <v>753</v>
       </c>
-      <c r="R26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>762</v>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" s="4" t="n">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="W26" s="4">
+        <f>SUM(C26:Q26)-R26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Kurikyal</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="D27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="E27" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>484</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" s="4" t="n">
         <v>0</v>
       </c>
@@ -2085,76 +2316,82 @@
         <v>0</v>
       </c>
       <c r="K27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" s="4" t="n">
         <v>701</v>
       </c>
-      <c r="R27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>711</v>
       </c>
-      <c r="U27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V27" s="4" t="n">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="W27" s="4">
+        <f>SUM(C27:Q27)-R27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Kurikyal</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="D28" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="E28" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="E28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="H28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" s="4" t="n">
         <v>0</v>
       </c>
@@ -2162,60 +2399,66 @@
         <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>659</v>
       </c>
-      <c r="R28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4" t="n">
         <v>668</v>
       </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V28" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="W28" s="4">
+        <f>SUM(C28:Q28)-R28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Kurikyal</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>380</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I29" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>0</v>
@@ -2230,63 +2473,69 @@
         <v>0</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O29" s="4" t="n">
         <v>13</v>
       </c>
       <c r="P29" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="R29" s="4" t="n">
         <v>524</v>
       </c>
-      <c r="R29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>532</v>
       </c>
-      <c r="U29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V29" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="W29" s="4">
+        <f>SUM(C29:Q29)-R29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Kondannapalli</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="D30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>146</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>516</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I30" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J30" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
@@ -2298,66 +2547,72 @@
         <v>0</v>
       </c>
       <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="O30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>782</v>
       </c>
-      <c r="R30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>790</v>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V30" s="4" t="n">
-        <v>-38</v>
+        <v>0</v>
+      </c>
+      <c r="W30" s="4">
+        <f>SUM(C30:Q30)-R30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>0</v>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Mallapur</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>369</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>327</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>0</v>
@@ -2366,194 +2621,212 @@
         <v>0</v>
       </c>
       <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="P31" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>836</v>
       </c>
-      <c r="R31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>841</v>
       </c>
-      <c r="U31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V31" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
+      </c>
+      <c r="W31" s="4">
+        <f>SUM(C31:Q31)-R31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>44</v>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Mallapur</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
         <v>44</v>
       </c>
       <c r="D32" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="n">
         <v>146</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>181</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I32" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="P32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="R32" s="4" t="n">
         <v>401</v>
       </c>
-      <c r="R32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>405</v>
       </c>
-      <c r="U32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" s="4" t="n">
-        <v>83</v>
+        <v>0</v>
+      </c>
+      <c r="W32" s="4">
+        <f>SUM(C32:Q32)-R32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>45</v>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Gopalraopally H/o Mallapur</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>45</v>
       </c>
       <c r="D33" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>265</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="P33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>478</v>
       </c>
-      <c r="R33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="U33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" s="4" t="n">
-        <v>-69</v>
+        <v>0</v>
+      </c>
+      <c r="W33" s="4">
+        <f>SUM(C33:Q33)-R33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Uppermallial</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="D34" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="E34" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="4" t="n">
         <v>0</v>
       </c>
@@ -2567,67 +2840,73 @@
         <v>0</v>
       </c>
       <c r="M34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Q34" s="4" t="n">
+      <c r="R34" s="4" t="n">
         <v>433</v>
       </c>
-      <c r="R34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>445</v>
       </c>
-      <c r="U34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V34" s="4" t="n">
-        <v>-101</v>
+        <v>0</v>
+      </c>
+      <c r="W34" s="4">
+        <f>SUM(C34:Q34)-R34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Uppermallial</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" s="4" t="n">
         <v>0</v>
       </c>
@@ -2635,273 +2914,297 @@
         <v>0</v>
       </c>
       <c r="M35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="O35" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="4" t="n">
+      <c r="R35" s="4" t="n">
         <v>543</v>
       </c>
-      <c r="R35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="U35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V35" s="4" t="n">
-        <v>-234</v>
+        <v>0</v>
+      </c>
+      <c r="W35" s="4">
+        <f>SUM(C35:Q35)-R35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Uppermallial</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="D36" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="E36" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>314</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="K36" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="L36" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O36" s="4" t="n">
+      <c r="P36" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q36" s="4" t="n">
+      <c r="R36" s="4" t="n">
         <v>609</v>
       </c>
-      <c r="R36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>616</v>
       </c>
-      <c r="U36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V36" s="4" t="n">
-        <v>399</v>
+        <v>0</v>
+      </c>
+      <c r="W36" s="4">
+        <f>SUM(C36:Q36)-R36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Rangaraopalli H/o Uppermallial</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="D37" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="D37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="P37" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>372</v>
       </c>
-      <c r="U37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V37" s="4" t="n">
-        <v>479</v>
+        <v>0</v>
+      </c>
+      <c r="W37" s="4">
+        <f>SUM(C37:Q37)-R37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Gattubuthkur</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="D38" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="E38" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>318</v>
       </c>
-      <c r="H38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N38" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O38" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P38" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q38" s="4" t="n">
+      <c r="R38" s="4" t="n">
         <v>1600</v>
       </c>
-      <c r="R38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>-751</v>
+        <v>0</v>
+      </c>
+      <c r="W38" s="4">
+        <f>SUM(C38:Q38)-R38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Gattubuthkur</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="D39" s="4" t="n">
         <v>202</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="E39" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>365</v>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="n">
         <v>0</v>
@@ -2916,40 +3219,46 @@
         <v>0</v>
       </c>
       <c r="P39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>688</v>
       </c>
-      <c r="U39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V39" s="4" t="n">
-        <v>1047</v>
+        <v>0</v>
+      </c>
+      <c r="W39" s="4">
+        <f>SUM(C39:Q39)-R39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Gattubuthkur</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>202</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="D40" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="D40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
@@ -2957,79 +3266,85 @@
         <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>303</v>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I40" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="O40" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="P40" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="Q40" s="4" t="n">
+      <c r="R40" s="4" t="n">
         <v>477</v>
       </c>
-      <c r="R40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="U40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V40" s="4" t="n">
-        <v>277</v>
+        <v>0</v>
+      </c>
+      <c r="W40" s="4">
+        <f>SUM(C40:Q40)-R40</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
         <v>334</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 334</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>225</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="D41" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="E41" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>363</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
@@ -3037,16 +3352,16 @@
         <v>0</v>
       </c>
       <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="4" t="n">
         <v>0</v>
@@ -3055,49 +3370,55 @@
         <v>0</v>
       </c>
       <c r="Q41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="4" t="n">
         <v>566</v>
       </c>
-      <c r="R41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4" t="n">
         <v>569</v>
       </c>
-      <c r="U41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V41" s="4" t="n">
-        <v>423</v>
+        <v>0</v>
+      </c>
+      <c r="W41" s="4">
+        <f>SUM(C41:Q41)-R41</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
         <v>335</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 335</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="D42" s="4" t="n">
         <v>227</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="E42" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
         <v>187</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>390</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I42" s="4" t="n">
         <v>0</v>
       </c>
@@ -3114,58 +3435,64 @@
         <v>0</v>
       </c>
       <c r="N42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="4" t="n">
         <v>648</v>
       </c>
-      <c r="R42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>654</v>
       </c>
-      <c r="U42" s="4" t="n">
+      <c r="V42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V42" s="4" t="n">
-        <v>421</v>
+      <c r="W42" s="4">
+        <f>SUM(C42:Q42)-R42</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
         <v>336</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 336</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>227</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="D43" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="E43" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
         <v>284</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>316</v>
       </c>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I43" s="4" t="n">
         <v>0</v>
       </c>
@@ -3173,11 +3500,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" s="4" t="n">
         <v>0</v>
       </c>
@@ -3185,55 +3512,61 @@
         <v>0</v>
       </c>
       <c r="O43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="P43" s="4" t="n">
+      <c r="Q43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q43" s="4" t="n">
+      <c r="R43" s="4" t="n">
         <v>809</v>
       </c>
-      <c r="R43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="U43" s="4" t="n">
         <v>835</v>
       </c>
-      <c r="U43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V43" s="4" t="n">
-        <v>432</v>
+        <v>0</v>
+      </c>
+      <c r="W43" s="4">
+        <f>SUM(C43:Q43)-R43</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
         <v>337</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 337</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="D44" s="4" t="n">
         <v>229</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="E44" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>309</v>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I44" s="4" t="n">
         <v>0</v>
       </c>
@@ -3259,119 +3592,131 @@
         <v>0</v>
       </c>
       <c r="Q44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="4" t="n">
         <v>862</v>
       </c>
-      <c r="R44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="T44" s="4" t="n">
+      <c r="U44" s="4" t="n">
         <v>877</v>
       </c>
-      <c r="U44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V44" s="4" t="n">
-        <v>285</v>
+        <v>0</v>
+      </c>
+      <c r="W44" s="4">
+        <f>SUM(C44:Q44)-R44</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
         <v>338</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 338</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
         <v>229</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="D45" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="E45" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>510</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I45" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="K45" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="L45" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="Q45" s="4" t="n">
+      <c r="R45" s="4" t="n">
         <v>921</v>
       </c>
-      <c r="R45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4" t="n">
         <v>931</v>
       </c>
-      <c r="U45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V45" s="4" t="n">
-        <v>426</v>
+        <v>0</v>
+      </c>
+      <c r="W45" s="4">
+        <f>SUM(C45:Q45)-R45</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
         <v>339</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 339</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="D46" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n">
         <v>336</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>249</v>
       </c>
-      <c r="H46" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I46" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -3386,61 +3731,67 @@
         <v>0</v>
       </c>
       <c r="N46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4" t="n">
         <v>492</v>
       </c>
-      <c r="R46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="4" t="n">
         <v>498</v>
       </c>
-      <c r="U46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V46" s="4" t="n">
-        <v>364</v>
+        <v>0</v>
+      </c>
+      <c r="W46" s="4">
+        <f>SUM(C46:Q46)-R46</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 340</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="D47" s="4" t="n">
         <v>232</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="E47" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="F47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>374</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J47" s="4" t="n">
         <v>0</v>
       </c>
@@ -3463,49 +3814,55 @@
         <v>0</v>
       </c>
       <c r="Q47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4" t="n">
         <v>611</v>
       </c>
-      <c r="R47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T47" s="4" t="n">
+      <c r="U47" s="4" t="n">
         <v>620</v>
       </c>
-      <c r="U47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V47" s="4" t="n">
-        <v>424</v>
+        <v>0</v>
+      </c>
+      <c r="W47" s="4">
+        <f>SUM(C47:Q47)-R47</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
         <v>341</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 341</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>232</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="D48" s="4" t="n">
         <v>233</v>
       </c>
-      <c r="D48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
         <v>451</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="H48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" s="4" t="n">
         <v>0</v>
       </c>
@@ -3522,58 +3879,64 @@
         <v>0</v>
       </c>
       <c r="N48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="O48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="4" t="n">
         <v>695</v>
       </c>
-      <c r="R48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="4" t="n">
         <v>712</v>
       </c>
-      <c r="U48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V48" s="4" t="n">
-        <v>664</v>
+        <v>0</v>
+      </c>
+      <c r="W48" s="4">
+        <f>SUM(C48:Q48)-R48</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
         <v>342</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 342</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
         <v>233</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="D49" s="4" t="n">
         <v>234</v>
       </c>
-      <c r="D49" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="E49" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>355</v>
       </c>
-      <c r="H49" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I49" s="4" t="n">
         <v>0</v>
       </c>
@@ -3608,315 +3971,345 @@
         <v>0</v>
       </c>
       <c r="T49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4" t="n">
         <v>532</v>
       </c>
-      <c r="U49" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V49" s="4" t="n">
-        <v>908</v>
+        <v>0</v>
+      </c>
+      <c r="W49" s="4">
+        <f>SUM(C49:Q49)-R49</f>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
         <v>343</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 343</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
         <v>234</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="D50" s="4" t="n">
         <v>235</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="E50" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="F50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>336</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="I50" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I50" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J50" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="O50" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="O50" s="4" t="n">
+      <c r="P50" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="P50" s="4" t="n">
+      <c r="Q50" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q50" s="4" t="n">
+      <c r="R50" s="4" t="n">
         <v>635</v>
       </c>
-      <c r="R50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="T50" s="4" t="n">
+      <c r="U50" s="4" t="n">
         <v>648</v>
       </c>
-      <c r="U50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V50" s="4" t="n">
-        <v>467</v>
+        <v>0</v>
+      </c>
+      <c r="W50" s="4">
+        <f>SUM(C50:Q50)-R50</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
         <v>344</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 344</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
         <v>235</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="D51" s="4" t="n">
         <v>236</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="E51" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="F51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>458</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O51" s="4" t="n">
+      <c r="P51" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P51" s="4" t="n">
+      <c r="Q51" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Q51" s="4" t="n">
+      <c r="R51" s="4" t="n">
         <v>607</v>
       </c>
-      <c r="R51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T51" s="4" t="n">
+      <c r="U51" s="4" t="n">
         <v>613</v>
       </c>
-      <c r="U51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V51" s="4" t="n">
-        <v>471</v>
+        <v>0</v>
+      </c>
+      <c r="W51" s="4">
+        <f>SUM(C51:Q51)-R51</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
         <v>345</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 345</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
         <v>236</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="D52" s="4" t="n">
         <v>237</v>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E52" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>583</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="I52" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L52" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="O52" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="4" t="n">
         <v>806</v>
       </c>
-      <c r="R52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="T52" s="4" t="n">
+      <c r="U52" s="4" t="n">
         <v>813</v>
       </c>
-      <c r="U52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V52" s="4" t="n">
-        <v>386</v>
+        <v>0</v>
+      </c>
+      <c r="W52" s="4">
+        <f>SUM(C52:Q52)-R52</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
         <v>346</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 346</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
         <v>237</v>
       </c>
-      <c r="C53" s="4" t="n">
+      <c r="D53" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="E53" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="E53" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F53" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>331</v>
       </c>
-      <c r="H53" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I53" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O53" s="4" t="n">
+      <c r="P53" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="P53" s="4" t="n">
+      <c r="Q53" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q53" s="4" t="n">
+      <c r="R53" s="4" t="n">
         <v>476</v>
       </c>
-      <c r="R53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="T53" s="4" t="n">
+      <c r="U53" s="4" t="n">
         <v>483</v>
       </c>
-      <c r="U53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V53" s="4" t="n">
-        <v>475</v>
+        <v>0</v>
+      </c>
+      <c r="W53" s="4">
+        <f>SUM(C53:Q53)-R53</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
         <v>347</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 347</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="D54" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="E54" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="E54" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>456</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="I54" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" s="4" t="n">
         <v>0</v>
       </c>
@@ -3930,261 +4323,285 @@
         <v>0</v>
       </c>
       <c r="N54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O54" s="4" t="n">
+      <c r="P54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P54" s="4" t="n">
+      <c r="Q54" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q54" s="4" t="n">
+      <c r="R54" s="4" t="n">
         <v>614</v>
       </c>
-      <c r="R54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="T54" s="4" t="n">
+      <c r="U54" s="4" t="n">
         <v>629</v>
       </c>
-      <c r="U54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V54" s="4" t="n">
-        <v>473</v>
+        <v>0</v>
+      </c>
+      <c r="W54" s="4">
+        <f>SUM(C54:Q54)-R54</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
         <v>348</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 348</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="D55" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="E55" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="F55" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>581</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="J55" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J55" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="K55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>7</v>
       </c>
       <c r="O55" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P55" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P55" s="4" t="n">
+      <c r="Q55" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="Q55" s="4" t="n">
+      <c r="R55" s="4" t="n">
         <v>728</v>
       </c>
-      <c r="R55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T55" s="4" t="n">
+      <c r="U55" s="4" t="n">
         <v>838</v>
       </c>
-      <c r="U55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V55" s="4" t="n">
-        <v>579</v>
+        <v>0</v>
+      </c>
+      <c r="W55" s="4">
+        <f>SUM(C55:Q55)-R55</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
         <v>349</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 349</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="D56" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="E56" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="F56" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>355</v>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="O56" s="4" t="n">
+      <c r="P56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="P56" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="Q56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" s="4" t="n">
         <v>619</v>
       </c>
-      <c r="R56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T56" s="4" t="n">
+      <c r="U56" s="4" t="n">
         <v>625</v>
       </c>
-      <c r="U56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V56" s="4" t="n">
-        <v>481</v>
+        <v>0</v>
+      </c>
+      <c r="W56" s="4">
+        <f>SUM(C56:Q56)-R56</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 350</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="D57" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="E57" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="E57" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>362</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J57" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M57" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q57" s="4" t="n">
+      <c r="R57" s="4" t="n">
         <v>563</v>
       </c>
-      <c r="R57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T57" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>566</v>
       </c>
-      <c r="U57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V57" s="4" t="n">
-        <v>483</v>
+        <v>0</v>
+      </c>
+      <c r="W57" s="4">
+        <f>SUM(C57:Q57)-R57</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
         <v>351</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 351</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="D58" s="4" t="n">
         <v>243</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="E58" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>364</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>1</v>
@@ -4193,137 +4610,149 @@
         <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="O58" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>6</v>
       </c>
       <c r="Q58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R58" s="4" t="n">
         <v>586</v>
       </c>
-      <c r="R58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="T58" s="4" t="n">
+      <c r="U58" s="4" t="n">
         <v>591</v>
       </c>
-      <c r="U58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V58" s="4" t="n">
-        <v>484</v>
+        <v>0</v>
+      </c>
+      <c r="W58" s="4">
+        <f>SUM(C58:Q58)-R58</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
         <v>352</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 352</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>243</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="D59" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>679</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="I59" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="J59" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="K59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O59" s="4" t="n">
+      <c r="P59" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="P59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="4" t="n">
         <v>943</v>
       </c>
-      <c r="R59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="4" t="n">
         <v>949</v>
       </c>
-      <c r="U59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V59" s="4" t="n">
-        <v>477</v>
+        <v>0</v>
+      </c>
+      <c r="W59" s="4">
+        <f>SUM(C59:Q59)-R59</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
         <v>353</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 353</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="D60" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="E60" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
         <v>432</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="I60" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>1</v>
@@ -4332,200 +4761,218 @@
         <v>1</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O60" s="4" t="n">
+      <c r="P60" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="P60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="4" t="n">
         <v>343</v>
       </c>
-      <c r="R60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" s="4" t="n">
         <v>345</v>
       </c>
-      <c r="U60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V60" s="4" t="n">
-        <v>778</v>
+        <v>0</v>
+      </c>
+      <c r="W60" s="4">
+        <f>SUM(C60:Q60)-R60</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
         <v>354</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 354</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="D61" s="4" t="n">
         <v>246</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="E61" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
         <v>279</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>369</v>
       </c>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K61" s="4" t="n">
+      <c r="L61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M61" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="O61" s="4" t="n">
+      <c r="P61" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="P61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="4" t="n">
         <v>729</v>
       </c>
-      <c r="R61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="T61" s="4" t="n">
+      <c r="U61" s="4" t="n">
         <v>741</v>
       </c>
-      <c r="U61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V61" s="4" t="n">
-        <v>446</v>
+        <v>0</v>
+      </c>
+      <c r="W61" s="4">
+        <f>SUM(C61:Q61)-R61</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
         <v>355</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 355</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
         <v>246</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="D62" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="E62" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="F62" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>307</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>304</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="J62" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="4" t="n">
         <v>651</v>
       </c>
-      <c r="R62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="T62" s="4" t="n">
+      <c r="U62" s="4" t="n">
         <v>661</v>
       </c>
-      <c r="U62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V62" s="4" t="n">
-        <v>514</v>
+        <v>0</v>
+      </c>
+      <c r="W62" s="4">
+        <f>SUM(C62:Q62)-R62</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
         <v>356</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 356</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="D63" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="E63" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E63" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F63" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="H63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I63" s="4" t="n">
         <v>0</v>
       </c>
@@ -4533,64 +4980,70 @@
         <v>0</v>
       </c>
       <c r="K63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="R63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="T63" s="4" t="n">
+      <c r="U63" s="4" t="n">
         <v>427</v>
       </c>
-      <c r="U63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V63" s="4" t="n">
-        <v>483</v>
+        <v>0</v>
+      </c>
+      <c r="W63" s="4">
+        <f>SUM(C63:Q63)-R63</f>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
         <v>357</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 357</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="D64" s="4" t="n">
         <v>249</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="E64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="G64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" s="4" t="n">
         <v>0</v>
       </c>
@@ -4601,10 +5054,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="4" t="n">
         <v>0</v>
@@ -4613,67 +5066,73 @@
         <v>0</v>
       </c>
       <c r="O64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="P64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="4" t="n">
         <v>709</v>
       </c>
-      <c r="R64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="4" t="n">
         <v>714</v>
       </c>
-      <c r="U64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V64" s="4" t="n">
-        <v>-146</v>
+        <v>0</v>
+      </c>
+      <c r="W64" s="4">
+        <f>SUM(C64:Q64)-R64</f>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
         <v>358</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 358</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
         <v>249</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="D65" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="E65" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>399</v>
       </c>
-      <c r="H65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" s="4" t="n">
         <v>0</v>
       </c>
@@ -4687,49 +5146,55 @@
         <v>0</v>
       </c>
       <c r="Q65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="4" t="n">
         <v>672</v>
       </c>
-      <c r="R65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="T65" s="4" t="n">
+      <c r="U65" s="4" t="n">
         <v>684</v>
       </c>
-      <c r="U65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V65" s="4" t="n">
-        <v>460</v>
+        <v>0</v>
+      </c>
+      <c r="W65" s="4">
+        <f>SUM(C65:Q65)-R65</f>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
         <v>359</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 359</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="D66" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="E66" s="4" t="n">
         <v>442</v>
       </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>426</v>
       </c>
-      <c r="H66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I66" s="4" t="n">
         <v>0</v>
       </c>
@@ -4755,49 +5220,55 @@
         <v>0</v>
       </c>
       <c r="Q66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="4" t="n">
         <v>743</v>
       </c>
-      <c r="R66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T66" s="4" t="n">
+      <c r="U66" s="4" t="n">
         <v>749</v>
       </c>
-      <c r="U66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V66" s="4" t="n">
-        <v>760</v>
+        <v>0</v>
+      </c>
+      <c r="W66" s="4">
+        <f>SUM(C66:Q66)-R66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
         <v>360</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 360</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
         <v>254</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="D67" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4" t="n">
         <v>451</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I67" s="4" t="n">
         <v>0</v>
       </c>
@@ -4823,49 +5294,55 @@
         <v>0</v>
       </c>
       <c r="Q67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="4" t="n">
         <v>556</v>
       </c>
-      <c r="R67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="T67" s="4" t="n">
+      <c r="U67" s="4" t="n">
         <v>561</v>
       </c>
-      <c r="U67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V67" s="4" t="n">
-        <v>438</v>
+        <v>0</v>
+      </c>
+      <c r="W67" s="4">
+        <f>SUM(C67:Q67)-R67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
         <v>361</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 361</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="D68" s="4" t="n">
         <v>253</v>
       </c>
-      <c r="D68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="H68" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="H68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
@@ -4885,55 +5362,61 @@
         <v>0</v>
       </c>
       <c r="O68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="4" t="n">
         <v>484</v>
       </c>
-      <c r="R68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T68" s="4" t="n">
+      <c r="U68" s="4" t="n">
         <v>490</v>
       </c>
-      <c r="U68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V68" s="4" t="n">
-        <v>449</v>
+        <v>0</v>
+      </c>
+      <c r="W68" s="4">
+        <f>SUM(C68:Q68)-R68</f>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
         <v>362</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Choppadandi PS 362</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
         <v>253</v>
       </c>
-      <c r="C69" s="4" t="n">
+      <c r="D69" s="4" t="n">
         <v>254</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="E69" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I69" s="4" t="n">
         <v>0</v>
       </c>
@@ -4959,108 +5442,280 @@
         <v>0</v>
       </c>
       <c r="Q69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="R69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T69" s="4" t="n">
+      <c r="U69" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="U69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V69" s="4" t="n">
-        <v>432</v>
+        <v>0</v>
+      </c>
+      <c r="W69" s="4">
+        <f>SUM(C69:Q69)-R69</f>
+        <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B70" s="6">
-        <f>SUM(B6:B69)</f>
-        <v/>
-      </c>
-      <c r="C70" s="6">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr"/>
+      <c r="C70" s="8">
         <f>SUM(C6:C69)</f>
         <v/>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="8">
         <f>SUM(D6:D69)</f>
         <v/>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="8">
         <f>SUM(E6:E69)</f>
         <v/>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="8">
         <f>SUM(F6:F69)</f>
         <v/>
       </c>
-      <c r="G70" s="6">
+      <c r="G70" s="8">
         <f>SUM(G6:G69)</f>
         <v/>
       </c>
-      <c r="H70" s="6">
+      <c r="H70" s="8">
         <f>SUM(H6:H69)</f>
         <v/>
       </c>
-      <c r="I70" s="6">
+      <c r="I70" s="8">
         <f>SUM(I6:I69)</f>
         <v/>
       </c>
-      <c r="J70" s="6">
+      <c r="J70" s="8">
         <f>SUM(J6:J69)</f>
         <v/>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="8">
         <f>SUM(K6:K69)</f>
         <v/>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="8">
         <f>SUM(L6:L69)</f>
         <v/>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="8">
         <f>SUM(M6:M69)</f>
         <v/>
       </c>
-      <c r="N70" s="6">
+      <c r="N70" s="8">
         <f>SUM(N6:N69)</f>
         <v/>
       </c>
-      <c r="O70" s="6">
+      <c r="O70" s="8">
         <f>SUM(O6:O69)</f>
         <v/>
       </c>
-      <c r="P70" s="6">
+      <c r="P70" s="8">
         <f>SUM(P6:P69)</f>
         <v/>
       </c>
-      <c r="Q70" s="6">
+      <c r="Q70" s="8">
         <f>SUM(Q6:Q69)</f>
         <v/>
       </c>
-      <c r="R70" s="6">
+      <c r="R70" s="8">
         <f>SUM(R6:R69)</f>
         <v/>
       </c>
-      <c r="S70" s="6">
+      <c r="S70" s="8">
         <f>SUM(S6:S69)</f>
         <v/>
       </c>
-      <c r="T70" s="6">
+      <c r="T70" s="8">
         <f>SUM(T6:T69)</f>
         <v/>
       </c>
-      <c r="U70" s="6">
+      <c r="U70" s="8">
         <f>SUM(U6:U69)</f>
+        <v/>
+      </c>
+      <c r="V70" s="8">
+        <f>SUM(V6:V69)</f>
+        <v/>
+      </c>
+      <c r="W70" s="8">
+        <f>SUM(W6:W69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr"/>
+      <c r="C71" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>247</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="S71" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="T71" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" s="10" t="n">
+        <v>435</v>
+      </c>
+      <c r="V71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr"/>
+      <c r="C72" s="12">
+        <f>C70+C71</f>
+        <v/>
+      </c>
+      <c r="D72" s="12">
+        <f>D70+D71</f>
+        <v/>
+      </c>
+      <c r="E72" s="12">
+        <f>E70+E71</f>
+        <v/>
+      </c>
+      <c r="F72" s="12">
+        <f>F70+F71</f>
+        <v/>
+      </c>
+      <c r="G72" s="12">
+        <f>G70+G71</f>
+        <v/>
+      </c>
+      <c r="H72" s="12">
+        <f>H70+H71</f>
+        <v/>
+      </c>
+      <c r="I72" s="12">
+        <f>I70+I71</f>
+        <v/>
+      </c>
+      <c r="J72" s="12">
+        <f>J70+J71</f>
+        <v/>
+      </c>
+      <c r="K72" s="12">
+        <f>K70+K71</f>
+        <v/>
+      </c>
+      <c r="L72" s="12">
+        <f>L70+L71</f>
+        <v/>
+      </c>
+      <c r="M72" s="12">
+        <f>M70+M71</f>
+        <v/>
+      </c>
+      <c r="N72" s="12">
+        <f>N70+N71</f>
+        <v/>
+      </c>
+      <c r="O72" s="12">
+        <f>O70+O71</f>
+        <v/>
+      </c>
+      <c r="P72" s="12">
+        <f>P70+P71</f>
+        <v/>
+      </c>
+      <c r="Q72" s="12">
+        <f>Q70+Q71</f>
+        <v/>
+      </c>
+      <c r="R72" s="12">
+        <f>R70+R71</f>
+        <v/>
+      </c>
+      <c r="S72" s="12">
+        <f>S70+S71</f>
+        <v/>
+      </c>
+      <c r="T72" s="12">
+        <f>T70+T71</f>
+        <v/>
+      </c>
+      <c r="U72" s="12">
+        <f>U70+U71</f>
+        <v/>
+      </c>
+      <c r="V72" s="12">
+        <f>V70+V71</f>
+        <v/>
+      </c>
+      <c r="W72" s="12">
+        <f>W70+W71</f>
         <v/>
       </c>
     </row>
